--- a/src/rodos_corpus/data/corpus/rendered/finance/REESTR-KA-2026.xlsx
+++ b/src/rodos_corpus/data/corpus/rendered/finance/REESTR-KA-2026.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1538,6 +1538,162 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>АО «Волга-Редуктор»</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>006316445577</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Самара</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>покупатель</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>ВР-2026/03</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>16.03.2026</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>31.12.2027</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>предоплата 40 % по счёту, остальное в течение 10 календарных дней после уведомления о готовности к отгрузке</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>30.07.2026</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>пройдена</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ООО «Сибгидромаш»</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>005503221144</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Омск</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>покупатель</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>СГМ-2026/05</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>12.05.2026</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>30.06.2027</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>предоплата 35 % по счёту, остальное в течение 5 банковских дней после отгрузки</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>23.01.2026</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>пройдена</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ООО «Балтмашкомплект»</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>007806334455</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Санкт-Петербург</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>покупатель</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>БМК-2025/11</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>24.11.2025</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>23.11.2027</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>предоплата 100 % по счёту</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>29.05.2026</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>пройдена</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
